--- a/output/country_profile.xlsx
+++ b/output/country_profile.xlsx
@@ -3713,7 +3713,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-20T10:05:08+09:00</t>
+          <t>2026-10-20T14:15:20+09:00</t>
         </is>
       </c>
     </row>
